--- a/AAII_Financials/Quarterly/KNTK_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/KNTK_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="92">
   <si>
     <t>KNTK</t>
   </si>
@@ -656,365 +656,378 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AB102"/>
+  <dimension ref="A5:AC102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
     </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>581400</v>
+      </c>
+      <c r="E8" s="3">
         <v>410000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>430400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>464000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>426700</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>443300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>385700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>396400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>359500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>341400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>348900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>330300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>296200</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>281000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>295500</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>325200</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>335600</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>257200</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>56300</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>34500</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>35600</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>34100</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>35300</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>40200</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>73000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>40900</v>
       </c>
     </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>309500</v>
+      </c>
+      <c r="E9" s="3">
         <v>259000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>234600</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>305800</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>224700</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>287000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>229700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>199000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>190600</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>197100</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>184300</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>190700</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>150400</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>151900</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>124400</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>151100</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>158600</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>124400</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>20600</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>9600</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>10700</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>9400</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>19100</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>18900</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>40200</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>21000</v>
       </c>
     </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>271900</v>
+      </c>
+      <c r="E10" s="3">
         <v>151000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>195800</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>158100</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>202000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>156300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>156000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>197400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>168900</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>144300</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>164500</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>139600</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>145800</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>129200</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>171100</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>174100</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>177000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>132800</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>35700</v>
-      </c>
-      <c r="V10" s="3">
-        <v>24900</v>
       </c>
       <c r="W10" s="3">
         <v>24900</v>
       </c>
       <c r="X10" s="3">
+        <v>24900</v>
+      </c>
+      <c r="Y10" s="3">
         <v>24700</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>16200</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>21300</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>32800</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>19900</v>
       </c>
     </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1043,8 +1056,9 @@
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
-    </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC11" s="3"/>
+    </row>
+    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1123,8 +1137,11 @@
       <c r="AB12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1203,8 +1220,11 @@
       <c r="AB13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1212,141 +1232,144 @@
         <v>0</v>
       </c>
       <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3">
         <v>-394100</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>5800</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>600</v>
       </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
       <c r="I14" s="3">
+        <v>0</v>
+      </c>
+      <c r="J14" s="3">
         <v>12400</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-28600</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-59400</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>4200</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>7700</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>2900</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>12100</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>400</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
       <c r="R14" s="3">
         <v>0</v>
       </c>
       <c r="S14" s="3">
+        <v>0</v>
+      </c>
+      <c r="T14" s="3">
         <v>22900</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>-4500</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>160400</v>
       </c>
-      <c r="V14" s="3">
-        <v>0</v>
-      </c>
       <c r="W14" s="3">
         <v>0</v>
       </c>
       <c r="X14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="3">
         <v>400</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>1600</v>
       </c>
-      <c r="Z14" s="3">
-        <v>0</v>
-      </c>
       <c r="AA14" s="3">
         <v>0</v>
       </c>
       <c r="AB14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>103300</v>
+      </c>
+      <c r="E15" s="3">
         <v>101800</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>100800</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>95400</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>93800</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>92700</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>87900</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>87600</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>75100</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>73600</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>72700</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>69900</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>69500</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>68900</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>67700</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>65000</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>66600</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>61000</v>
-      </c>
-      <c r="U15" s="3">
-        <v>4100</v>
       </c>
       <c r="V15" s="3">
         <v>4100</v>
       </c>
       <c r="W15" s="3">
-        <v>4000</v>
+        <v>4100</v>
       </c>
       <c r="X15" s="3">
         <v>4000</v>
@@ -1358,13 +1381,16 @@
         <v>4000</v>
       </c>
       <c r="AA15" s="3">
+        <v>4000</v>
+      </c>
+      <c r="AB15" s="3">
         <v>8000</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>3900</v>
       </c>
     </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1390,168 +1416,175 @@
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
-    </row>
-    <row r="17" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC16" s="3"/>
+    </row>
+    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>447500</v>
+      </c>
+      <c r="E17" s="3">
         <v>413800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>360700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>438400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>349300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>424000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>349600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>322100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>302900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>311100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>286900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>289000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>246600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>253400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>250500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>279400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>317800</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>233700</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>192400</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>20000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>22000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>21100</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>23000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>21200</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>42500</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>22200</v>
       </c>
     </row>
-    <row r="18" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>133900</v>
+      </c>
+      <c r="E18" s="3">
         <v>-3900</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>69700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>25500</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>77400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>19200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>36100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>74300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>56500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>30300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>61900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>41300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>49600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>27600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>45000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>45800</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>17800</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>23500</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-136100</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>14500</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>13600</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>13000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>12300</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>19000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>30500</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>18700</v>
       </c>
     </row>
-    <row r="19" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1580,385 +1613,398 @@
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
-    </row>
-    <row r="20" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC19" s="3"/>
+    </row>
+    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-57400</v>
+      </c>
+      <c r="E20" s="3">
         <v>-51200</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-54400</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-58300</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-61100</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-57500</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-44300</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-53200</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-56000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-60000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-51900</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-50800</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-49600</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-46500</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>60500</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>45500</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>139200</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>25300</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>92000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>37800</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>62800</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>12100</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>48800</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>12600</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-39900</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-44500</v>
       </c>
     </row>
-    <row r="21" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>294700</v>
+      </c>
+      <c r="E21" s="3">
         <v>149200</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>224800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>179200</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>232300</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>169400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>168400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>215100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>187500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>163900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>186500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>162000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>168700</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>143000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>173200</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>156300</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>223500</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>109900</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-40000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>56400</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>80500</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>29100</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>65000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>35600</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-1500</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>-21900</v>
       </c>
     </row>
-    <row r="22" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>54100</v>
+      </c>
+      <c r="E22" s="3">
         <v>53400</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>59400</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>61700</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>56500</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>55700</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>49700</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>66000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>54000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>47500</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>75400</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>45000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>16100</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>69300</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>56700</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>40500</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>25300</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>26800</v>
-      </c>
-      <c r="U22" s="3">
-        <v>2700</v>
       </c>
       <c r="V22" s="3">
         <v>2700</v>
       </c>
       <c r="W22" s="3">
-        <v>2600</v>
+        <v>2700</v>
       </c>
       <c r="X22" s="3">
         <v>2600</v>
       </c>
       <c r="Y22" s="3">
+        <v>2600</v>
+      </c>
+      <c r="Z22" s="3">
         <v>1200</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>400</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>600</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="23" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>137500</v>
+      </c>
+      <c r="E23" s="3">
         <v>-5900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>456400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>16700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>81700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>21800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>18000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>91900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>118200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>39200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>32400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>44400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>72000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>4700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>48800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>50800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>131600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>22100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-46800</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>49700</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>73800</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>22500</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>59800</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>31200</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-10000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-26100</v>
       </c>
     </row>
-    <row r="24" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>14400</v>
+      </c>
+      <c r="E24" s="3">
         <v>-800</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>39700</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>1100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>7300</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>2600</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>1800</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>8300</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>9200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>3800</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-234900</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>1300</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>300</v>
-      </c>
-      <c r="P24" s="3">
-        <v>400</v>
       </c>
       <c r="Q24" s="3">
         <v>400</v>
       </c>
       <c r="R24" s="3">
+        <v>400</v>
+      </c>
+      <c r="S24" s="3">
         <v>1400</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>200</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>700</v>
       </c>
-      <c r="U24" s="3">
-        <v>0</v>
-      </c>
       <c r="V24" s="3">
         <v>0</v>
       </c>
@@ -1975,13 +2021,16 @@
         <v>0</v>
       </c>
       <c r="AA24" s="3">
-        <v>-700</v>
+        <v>0</v>
       </c>
       <c r="AB24" s="3">
         <v>-700</v>
       </c>
-    </row>
-    <row r="25" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC24" s="3">
+        <v>-700</v>
+      </c>
+    </row>
+    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2060,168 +2109,177 @@
       <c r="AB25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>123100</v>
+      </c>
+      <c r="E26" s="3">
         <v>-5100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>416700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>15500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>74400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>19300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>16200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>83700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>108900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>35400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>267400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>43100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>71700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>4300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>48500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>49400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>131400</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>21400</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-46800</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>49700</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>73800</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>22500</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>59800</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>31200</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-9300</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-25400</v>
       </c>
     </row>
-    <row r="27" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>48600</v>
+      </c>
+      <c r="E27" s="3">
         <v>-4800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>139800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>1900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>20200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>2800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>21000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>32600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>7200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>243000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>11200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>20600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-2700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>11300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>43700</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>2300</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>3900</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-31000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>5200</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>11700</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>200</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>8900</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>2900</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-9000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-8100</v>
       </c>
     </row>
-    <row r="28" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2300,8 +2358,11 @@
       <c r="AB28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2380,8 +2441,11 @@
       <c r="AB29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2460,8 +2524,11 @@
       <c r="AB30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2540,168 +2607,177 @@
       <c r="AB31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>57400</v>
+      </c>
+      <c r="E32" s="3">
         <v>51200</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>54400</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>58300</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>61100</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>57500</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>44300</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>53200</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>56000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>60000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>51900</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>50800</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>49600</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>46500</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-60500</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-45500</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-139200</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-25300</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-92000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-37800</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-62800</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-12100</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-48800</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-12600</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>39900</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>44500</v>
       </c>
     </row>
-    <row r="33" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>123100</v>
+      </c>
+      <c r="E33" s="3">
         <v>-5100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>416700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>15500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>74400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>19300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>16200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>83700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>108900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>35400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>267400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>43100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>71700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>4300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>11300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>43700</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>2300</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>3900</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-31000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>5200</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>11700</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>200</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>8900</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>2900</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-9000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-8100</v>
       </c>
     </row>
-    <row r="34" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2780,173 +2856,182 @@
       <c r="AB34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>123100</v>
+      </c>
+      <c r="E35" s="3">
         <v>-5100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>416700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>15500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>74400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>19300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>16200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>83700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>108900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>35400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>267400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>43100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>71700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>4300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>11300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>43700</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>2300</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>3900</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-31000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>5200</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>11700</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>200</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>8900</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>2900</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-9000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-8100</v>
       </c>
     </row>
-    <row r="37" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
     </row>
-    <row r="39" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2975,8 +3060,9 @@
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
-    </row>
-    <row r="40" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC39" s="3"/>
+    </row>
+    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3005,130 +3091,134 @@
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
-    </row>
-    <row r="41" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC40" s="3"/>
+    </row>
+    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>7800</v>
+      </c>
+      <c r="E41" s="3">
         <v>700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>4000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>7700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>10700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>8800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>3600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>20400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>12500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>9800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>4500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>2200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>2000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>6400</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>11700</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>5300</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>17600</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>132000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>109000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>75100</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>51300</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>24200</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>2000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>1900</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>19300</v>
       </c>
     </row>
-    <row r="42" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>3400</v>
+      </c>
+      <c r="E42" s="3">
         <v>1600</v>
       </c>
-      <c r="E42" s="3">
-        <v>0</v>
-      </c>
       <c r="F42" s="3">
+        <v>0</v>
+      </c>
+      <c r="G42" s="3">
         <v>400</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>700</v>
-      </c>
-      <c r="H42" s="3">
-        <v>500</v>
       </c>
       <c r="I42" s="3">
         <v>500</v>
       </c>
       <c r="J42" s="3">
+        <v>500</v>
+      </c>
+      <c r="K42" s="3">
         <v>100</v>
       </c>
-      <c r="K42" s="3">
-        <v>0</v>
-      </c>
       <c r="L42" s="3">
         <v>0</v>
       </c>
       <c r="M42" s="3">
+        <v>0</v>
+      </c>
+      <c r="N42" s="3">
         <v>4300</v>
       </c>
-      <c r="N42" s="3">
-        <v>0</v>
-      </c>
       <c r="O42" s="3">
+        <v>0</v>
+      </c>
+      <c r="P42" s="3">
         <v>17800</v>
       </c>
-      <c r="P42" s="3">
-        <v>0</v>
-      </c>
       <c r="Q42" s="3">
         <v>0</v>
       </c>
@@ -3165,99 +3255,105 @@
       <c r="AB42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>60900</v>
+      </c>
+      <c r="E43" s="3">
         <v>92700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>85300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>77400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>62900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>122500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>111900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>70300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>99100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>209900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>215700</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>235300</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>181500</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>199000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>204000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>269600</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>296200</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>262600</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>25800</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>12000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>13700</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>13200</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>12900</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>13700</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>13600</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>12800</v>
       </c>
     </row>
-    <row r="44" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E44" s="3">
+      <c r="E44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F44" s="3">
         <v>4600</v>
-      </c>
-      <c r="F44" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="G44" s="3" t="s">
         <v>8</v>
@@ -3265,11 +3361,11 @@
       <c r="H44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I44" s="3">
+      <c r="I44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J44" s="3">
         <v>3600</v>
-      </c>
-      <c r="J44" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="K44" s="3" t="s">
         <v>8</v>
@@ -3277,432 +3373,447 @@
       <c r="L44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M44" s="3">
+      <c r="M44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N44" s="3">
         <v>3100</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>9100</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>7300</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>4700</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>4800</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>13100</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>13000</v>
       </c>
-      <c r="T44" s="3" t="s">
+      <c r="U44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>3000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>3300</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>3400</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>3900</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>3600</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>3700</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>3800</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>4200</v>
       </c>
     </row>
-    <row r="45" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>241300</v>
+      </c>
+      <c r="E45" s="3">
         <v>193100</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>179400</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>185700</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>201400</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>150600</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>142000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>156800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>160900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>10300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>3500</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>21600</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>9900</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>13800</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>26600</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>24300</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>27200</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>29200</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>5900</v>
-      </c>
-      <c r="V45" s="3">
-        <v>6000</v>
       </c>
       <c r="W45" s="3">
         <v>6000</v>
       </c>
       <c r="X45" s="3">
+        <v>6000</v>
+      </c>
+      <c r="Y45" s="3">
         <v>7800</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>2100</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>1000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>1700</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="46" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>349700</v>
+      </c>
+      <c r="E46" s="3">
         <v>318800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>302000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>315100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>312600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>315000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>294800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>285900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>299300</v>
-      </c>
-      <c r="L46" s="3">
-        <v>257300</v>
       </c>
       <c r="M46" s="3">
         <v>257300</v>
       </c>
       <c r="N46" s="3">
+        <v>257300</v>
+      </c>
+      <c r="O46" s="3">
         <v>288500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>247800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>246200</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>241900</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>318800</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>341800</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>309500</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>166600</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>130300</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>98200</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>76200</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>42800</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>20400</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>20900</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>37500</v>
       </c>
     </row>
-    <row r="47" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>1989300</v>
+      </c>
+      <c r="E47" s="3">
         <v>1993200</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>2008700</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>2085500</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>2105300</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>2112300</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>2117900</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>2142000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>2075900</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>2526300</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>2541000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>2519200</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>2490100</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>2412900</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>2381300</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>2372600</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>2342300</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>2361300</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>1364800</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>1537900</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>1554400</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>1566700</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>1555200</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>1524400</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>1408500</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>1336800</v>
       </c>
     </row>
-    <row r="48" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>3993500</v>
+      </c>
+      <c r="E48" s="3">
         <v>3948100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>3937400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>3891400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>3811400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>3675900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>3463700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>3265000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>3240200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>2774500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>2780800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>2768500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>2750500</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>2698300</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>2563800</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>2563300</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>2534100</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>2535100</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>187000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>189400</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>190800</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>193400</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>195800</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>205300</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>207300</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>208500</v>
       </c>
     </row>
-    <row r="49" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>498600</v>
+      </c>
+      <c r="E49" s="3">
         <v>528300</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>558300</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>589700</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>612800</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>638900</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>657600</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>883200</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>951700</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>567900</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>596700</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>625900</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>655000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>681600</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>700500</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>726900</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>751800</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>776900</v>
-      </c>
-      <c r="U49" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="V49" s="3" t="s">
         <v>8</v>
@@ -3716,8 +3827,8 @@
       <c r="Y49" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z49" s="3">
-        <v>0</v>
+      <c r="Z49" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AA49" s="3">
         <v>0</v>
@@ -3725,8 +3836,11 @@
       <c r="AB49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3805,8 +3919,11 @@
       <c r="AB50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3885,88 +4002,94 @@
       <c r="AB51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E52" s="3">
         <v>800</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>1500</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>1100</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>1900</v>
-      </c>
-      <c r="H52" s="3">
-        <v>100</v>
       </c>
       <c r="I52" s="3">
         <v>100</v>
       </c>
       <c r="J52" s="3">
+        <v>100</v>
+      </c>
+      <c r="K52" s="3">
         <v>1600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>100</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>200</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>2400</v>
       </c>
-      <c r="O52" s="3" t="s">
+      <c r="P52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>100</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>32300</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>25500</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>26400</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>30900</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>6200</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>8300</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>10300</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>6300</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>5800</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>6300</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>5500</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>5700</v>
       </c>
     </row>
-    <row r="53" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4045,88 +4168,94 @@
       <c r="AB53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>7202500</v>
+      </c>
+      <c r="E54" s="3">
         <v>7110700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>7095600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>7202100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>7151000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>7030700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>6814900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>6860500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>6860300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>6447600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>6496900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>6286000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>6226900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>6124700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>5919700</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>6007200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>5996300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>6013700</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>1724700</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>1865900</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>1853700</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>1842600</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>1799600</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>1756400</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>1642200</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>1588500</v>
       </c>
     </row>
-    <row r="55" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4155,8 +4284,9 @@
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
-    </row>
-    <row r="56" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC55" s="3"/>
+    </row>
+    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4185,64 +4315,65 @@
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
-    </row>
-    <row r="57" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC56" s="3"/>
+    </row>
+    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>48600</v>
+      </c>
+      <c r="E57" s="3">
         <v>28700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>42100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>31600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>36600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>38700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>27200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>17200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>44500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>16500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>34000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>17600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>36200</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>18300</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>17900</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>16000</v>
-      </c>
-      <c r="S57" s="3">
-        <v>10900</v>
       </c>
       <c r="T57" s="3">
         <v>10900</v>
       </c>
       <c r="U57" s="3">
-        <v>0</v>
+        <v>10900</v>
       </c>
       <c r="V57" s="3">
         <v>0</v>
@@ -4254,64 +4385,67 @@
         <v>0</v>
       </c>
       <c r="Y57" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z57" s="3">
         <v>18800</v>
       </c>
-      <c r="Z57" s="3" t="s">
+      <c r="AA57" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>200</v>
       </c>
-      <c r="AB57" s="3" t="s">
+      <c r="AC57" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="58" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>260500</v>
+      </c>
+      <c r="E58" s="3">
         <v>227100</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>208900</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>223200</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>231800</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>165100</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>160100</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>179400</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>181800</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>25000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>29200</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>33400</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>37800</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>39800</v>
       </c>
-      <c r="Q58" s="3">
-        <v>0</v>
-      </c>
       <c r="R58" s="3">
         <v>0</v>
       </c>
@@ -4319,10 +4453,10 @@
         <v>0</v>
       </c>
       <c r="T58" s="3">
+        <v>0</v>
+      </c>
+      <c r="U58" s="3">
         <v>54300</v>
-      </c>
-      <c r="U58" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="V58" s="3" t="s">
         <v>8</v>
@@ -4333,8 +4467,8 @@
       <c r="X58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y58" s="3">
-        <v>0</v>
+      <c r="Y58" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Z58" s="3">
         <v>0</v>
@@ -4345,224 +4479,233 @@
       <c r="AB58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>66200</v>
+      </c>
+      <c r="E59" s="3">
         <v>83100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>37900</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>62100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>70700</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>64400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>73500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>44500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>35300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>37300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>28700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>38800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>34200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>35500</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>209900</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>268700</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>295100</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>323400</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>27200</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>27500</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>25100</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>21900</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>11200</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>16500</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>11900</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>12700</v>
       </c>
     </row>
-    <row r="60" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>512400</v>
+      </c>
+      <c r="E60" s="3">
         <v>537100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>440500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>504300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>501800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>475300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>418600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>398700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>398900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>234000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>250100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>251100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>199400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>248300</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>227800</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>284700</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>306000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>388600</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>27200</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>27500</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>25100</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>21900</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>30000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>16500</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>12100</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>12700</v>
       </c>
     </row>
-    <row r="61" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>3716600</v>
+      </c>
+      <c r="E61" s="3">
         <v>3662300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>3656800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>3996200</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>3775000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>3588600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>3375500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>3292800</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>3273500</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>3520500</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>3577500</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>3622600</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>3647500</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>3536900</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>3368500</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>3447500</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>2971300</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>2894000</v>
-      </c>
-      <c r="U61" s="3">
-        <v>657000</v>
       </c>
       <c r="V61" s="3">
         <v>657000</v>
@@ -4574,99 +4717,105 @@
         <v>657000</v>
       </c>
       <c r="Y61" s="3">
+        <v>657000</v>
+      </c>
+      <c r="Z61" s="3">
         <v>624000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>580000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>493000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>468000</v>
       </c>
     </row>
-    <row r="62" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>800</v>
+      </c>
+      <c r="E62" s="3">
         <v>16500</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>14700</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>25100</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>24600</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>27600</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>4100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>68600</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>66800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>3300</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>3200</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>3700</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>7000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>31400</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>50700</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>47700</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>85800</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>222700</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>135300</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>193700</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>197500</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>227500</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>208600</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>247800</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>243500</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>232300</v>
       </c>
     </row>
-    <row r="63" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4745,8 +4894,11 @@
       <c r="AB63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4825,8 +4977,11 @@
       <c r="AB64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4905,88 +5060,94 @@
       <c r="AB65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>4290400</v>
+      </c>
+      <c r="E66" s="3">
         <v>4268600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>4165200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>4576900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>4340600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>4129800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>3835900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>3798000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>3777600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>3796400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>3869900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>3915500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>3890100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>3850000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>6759500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>6841700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>7177700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>7151500</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>2301900</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>2350100</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>2359900</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>2173600</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>2046100</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>1683600</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>1571900</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>1518000</v>
       </c>
     </row>
-    <row r="67" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5015,8 +5176,9 @@
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
-    </row>
-    <row r="68" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC67" s="3"/>
+    </row>
+    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5095,8 +5257,11 @@
       <c r="AB68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5175,8 +5340,11 @@
       <c r="AB69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5255,8 +5423,11 @@
       <c r="AB70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5335,88 +5506,94 @@
       <c r="AB71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-1680100</v>
+      </c>
+      <c r="E72" s="3">
         <v>-1669300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-806100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-1997700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-1781400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-2616600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-2976600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-1720700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-1206900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-973500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-723500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-929800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-902400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-863500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-958600</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-941700</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-1181300</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-1137900</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-577300</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-484100</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-506200</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-369300</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-391000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-400400</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-402700</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-402500</v>
       </c>
     </row>
-    <row r="73" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5495,8 +5672,11 @@
       <c r="AB73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5575,8 +5755,11 @@
       <c r="AB74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5655,88 +5838,94 @@
       <c r="AB75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-1185100</v>
+      </c>
+      <c r="E76" s="3">
         <v>-1669200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>-565400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>-1775700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>-1565700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>-2549700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>-2976600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>-1720700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>-1206900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>-973400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>-530800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>-838000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>-905800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>-636200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>-839800</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>-834600</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>-1181300</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>-1137900</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>-577200</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>-484100</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>-506200</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>-331000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>-246500</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>72800</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>70300</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>70500</v>
       </c>
     </row>
-    <row r="77" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5815,173 +6004,182 @@
       <c r="AB77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
     </row>
-    <row r="81" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>123100</v>
+      </c>
+      <c r="E81" s="3">
         <v>-5100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>416700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>15500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>74400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>19300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>16200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>83700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>108900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>35400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>267400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>43100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>71700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>4300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>11300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>43700</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>2300</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>3900</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-31000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>5200</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>11700</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>200</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>8900</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>2900</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-9000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-8100</v>
       </c>
     </row>
-    <row r="82" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6010,70 +6208,71 @@
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
-    </row>
-    <row r="83" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC82" s="3"/>
+    </row>
+    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>57100</v>
+      </c>
+      <c r="E83" s="3">
         <v>62100</v>
-      </c>
-      <c r="E83" s="3">
-        <v>48700</v>
       </c>
       <c r="F83" s="3">
         <v>48700</v>
       </c>
       <c r="G83" s="3">
+        <v>48700</v>
+      </c>
+      <c r="H83" s="3">
         <v>43800</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>42900</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>42000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>39400</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>38900</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>38400</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>37200</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>34900</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>36700</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>30800</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>67700</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>65000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>66600</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>61000</v>
-      </c>
-      <c r="U83" s="3">
-        <v>4100</v>
       </c>
       <c r="V83" s="3">
         <v>4100</v>
       </c>
       <c r="W83" s="3">
-        <v>4000</v>
+        <v>4100</v>
       </c>
       <c r="X83" s="3">
         <v>4000</v>
@@ -6085,13 +6284,16 @@
         <v>4000</v>
       </c>
       <c r="AA83" s="3">
+        <v>4000</v>
+      </c>
+      <c r="AB83" s="3">
         <v>8000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>3900</v>
       </c>
     </row>
-    <row r="84" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6170,8 +6372,11 @@
       <c r="AB84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6250,8 +6455,11 @@
       <c r="AB85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6330,8 +6538,11 @@
       <c r="AB86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6410,8 +6621,11 @@
       <c r="AB87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6490,88 +6704,94 @@
       <c r="AB88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>161100</v>
+      </c>
+      <c r="E89" s="3">
         <v>180400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>110100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>188100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>129100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>176800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>144000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>214100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>125500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>153700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>178900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>174500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>111500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>119600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>159800</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>184300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>170500</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>98400</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>51300</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>57300</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>57800</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>43300</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>26800</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>50700</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>86800</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>51500</v>
       </c>
     </row>
-    <row r="90" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6600,88 +6820,92 @@
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
-    </row>
-    <row r="91" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC90" s="3"/>
+    </row>
+    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-109200</v>
+      </c>
+      <c r="E91" s="3">
         <v>-83000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-134100</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-156500</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-127300</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-74500</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-107700</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-58500</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-39400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-58000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-67100</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-85600</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-101300</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-58900</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-47800</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-93900</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-47200</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-32800</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-1300</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-800</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-1100</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-1300</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-400</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-3000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-26500</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-19100</v>
       </c>
     </row>
-    <row r="92" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6760,8 +6984,11 @@
       <c r="AB92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6840,88 +7067,94 @@
       <c r="AB93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-115100</v>
+      </c>
+      <c r="E94" s="3">
         <v>-89100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>363800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-171300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-131500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-260100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-111000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-109200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>105300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-62000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-103700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-134700</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-201400</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-246500</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-69700</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-147400</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-49700</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-19400</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>7600</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>12500</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>1900</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-13200</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-37100</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-126000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-175300</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-97600</v>
       </c>
     </row>
-    <row r="95" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6950,64 +7183,65 @@
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
-    </row>
-    <row r="96" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC95" s="3"/>
+    </row>
+    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>131700</v>
+      </c>
+      <c r="E96" s="3">
         <v>131300</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>126300</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>126900</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>123700</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>123200</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>123000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>118200</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>115200</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>39500</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>23500</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>22000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>19600</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>16900</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-300</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-400</v>
       </c>
-      <c r="S96" s="3">
-        <v>0</v>
-      </c>
       <c r="T96" s="3">
         <v>0</v>
       </c>
       <c r="U96" s="3">
-        <v>-5600</v>
+        <v>0</v>
       </c>
       <c r="V96" s="3">
         <v>-5600</v>
@@ -7019,7 +7253,7 @@
         <v>-5600</v>
       </c>
       <c r="Y96" s="3">
-        <v>0</v>
+        <v>-5600</v>
       </c>
       <c r="Z96" s="3">
         <v>0</v>
@@ -7030,8 +7264,11 @@
       <c r="AB96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7110,8 +7347,11 @@
       <c r="AB97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7190,8 +7430,11 @@
       <c r="AB98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7270,64 +7513,67 @@
       <c r="AB99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-38900</v>
+      </c>
+      <c r="E100" s="3">
         <v>-94500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-477700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-19800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>4300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>88500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-49800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-97000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-228000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-86500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-70700</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-42000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>90200</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>122500</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-95400</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-30600</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-133200</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-80100</v>
-      </c>
-      <c r="U100" s="3">
-        <v>-35900</v>
       </c>
       <c r="V100" s="3">
         <v>-35900</v>
@@ -7336,22 +7582,25 @@
         <v>-35900</v>
       </c>
       <c r="X100" s="3">
+        <v>-35900</v>
+      </c>
+      <c r="Y100" s="3">
         <v>-2900</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>32400</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>75400</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>84400</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>59400</v>
       </c>
     </row>
-    <row r="101" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7394,8 +7643,8 @@
       <c r="P101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q101" s="3">
-        <v>0</v>
+      <c r="Q101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R101" s="3">
         <v>0</v>
@@ -7430,84 +7679,90 @@
       <c r="AB101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>7100</v>
+      </c>
+      <c r="E102" s="3">
         <v>-3200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-3800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-3000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>1900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>5200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-16800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>7900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>2800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>5200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>4400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-2200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-4400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-5300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>6400</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-12300</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-1100</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>23000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>33900</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>23800</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>27100</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>22200</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>100</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-4100</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>13300</v>
       </c>
     </row>
